--- a/output/_temp/etapa_1_limpieza_base/msewjo_limpio_tecnico.xlsx
+++ b/output/_temp/etapa_1_limpieza_base/msewjo_limpio_tecnico.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H232"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,346 +465,354 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03648736</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>03649003</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RF-4 SAN NICOLAS</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SIGADM</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46027</v>
+        <v>46128</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MEDICION DE RUIDO HUINQUINTIPA</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) RF-4 SAN NICOLAS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>RF-4 SAN NICOLAS</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SIGADM</t>
+          <t>SIGVA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>03648748</t>
+          <t>03649004</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ESTACION COPAQUIRE</t>
+          <t>RF-4 SAN NICOLAS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SIGAIR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46027</v>
+        <v>46128</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>OPERACIÓN DE ESTACIONES CONTINUAS ESTACION COPAQUIRE</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS RF-4 SAN NICOLAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ESTACION COPAQUIRE</t>
+          <t>RF-4 SAN NICOLAS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SIGAIR</t>
+          <t>SIGVA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>03648749</t>
+          <t>03649057</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ESTACION COPAQUIRE</t>
+          <t>MAH-01 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SIGAIR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46027</v>
+        <v>46128</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MANTENCION DE ESTACIONES CONTINUAS ESTACION COPAQUIRE</t>
+          <t>MEDICION DE NIVELES FREATICOS MAH-01 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ESTACION COPAQUIRE</t>
+          <t>MAH-01 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SIGAIR</t>
+          <t>SIGVA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>03648750</t>
+          <t>03649058</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rosario</t>
+          <t>MAH-01 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SIGAIR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OPERACIÓN ESTACIONES METEOROLOGICAS Rosario</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MAH-01 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rosario</t>
+          <t>MAH-01 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SIGAIR</t>
+          <t>SIGVA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>03648754</t>
+          <t>03649190</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sensor NE Piscina 4</t>
+          <t>QYA YABRICOYITA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46299</v>
+        <v>46128</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Limpieza narices elect Sensor NE Piscina 4</t>
+          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES QYA YABRICOYITA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sensor NE Piscina 4</t>
+          <t>QYA YABRICOYITA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>03648757</t>
+          <t>03649191</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sensor NE Piscina 2A</t>
+          <t>QYA YABRICOYITA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46299</v>
+        <v>46128</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Limpieza narices elect Sensor NE Piscina 2A</t>
+          <t>MEDICION DE CAUDAL QYA YABRICOYITA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sensor NE Piscina 2A</t>
+          <t>QYA YABRICOYITA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03648759</t>
+          <t>03649194</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sensor NE TK-33</t>
+          <t>PUNTERA 1 (P-01)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46299</v>
+        <v>46128</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Limpieza narices elect Sensor NE TK-33</t>
+          <t>MEDICION DE NIVELES FREATICOS PUNTERA 1 (P-01)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sensor NE TK-33</t>
+          <t>PUNTERA 1 (P-01)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>03648764</t>
+          <t>03649195</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sensor NE Piscina 3B</t>
+          <t>PUNTERA 1 (P-01)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46299</v>
+        <v>46128</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Limpieza narices elect Sensor NE Piscina 3B</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PUNTERA 1 (P-01)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sensor NE Piscina 3B</t>
+          <t>PUNTERA 1 (P-01)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>03648766</t>
+          <t>03649200</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sensor NE Piscina 10</t>
+          <t>PUNTERA 2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46299</v>
+        <v>46128</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Limpieza narices elect Sensor NE Piscina 10</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PUNTERA 2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sensor NE Piscina 10</t>
+          <t>PUNTERA 2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SIGNAR</t>
+          <t>SIGVA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03648877</t>
+          <t>03649201</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ADTR LIXIVIACIÓN</t>
+          <t>PUNTERA 2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -813,19 +821,19 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS ADTR LIXIVIACIÓN</t>
+          <t>MEDICIÓN NIVELES FREÁTICOS PUNTERA 2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ADTR LIXIVIACIÓN</t>
+          <t>PUNTERA 2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -837,12 +845,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03648878</t>
+          <t>03649212</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MTP-17 TRANQUE</t>
+          <t>RF-1 YABRICOLLITA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -851,19 +859,19 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MTP-17 TRANQUE</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) RF-1 YABRICOLLITA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MTP-17 TRANQUE</t>
+          <t>RF-1 YABRICOLLITA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -875,12 +883,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03648879</t>
+          <t>03649213</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MTP-17</t>
+          <t>RF-1 YABRICOLLITA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -889,19 +897,19 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) MTP-17</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS RF-1 YABRICOLLITA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MTP-17</t>
+          <t>RF-1 YABRICOLLITA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -913,12 +921,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03648880</t>
+          <t>03649214</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FAD PUERTO COLLAHUASI</t>
+          <t>RF-2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -927,19 +935,19 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MUESTREO EN PLANTA FAD FAD PUERTO COLLAHUASI</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) RF-2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FAD PUERTO COLLAHUASI</t>
+          <t>RF-2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -951,12 +959,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>03648881</t>
+          <t>03649215</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LPDC-01 LIXIVIACIÓN</t>
+          <t>RF-2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -965,19 +973,19 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS LPDC-01 LIXIVIACIÓN</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS RF-2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>LPDC-01 LIXIVIACIÓN</t>
+          <t>RF-2 SALLIHUINCA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -989,12 +997,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>03648882</t>
+          <t>03649222</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LPDC-01 LIXIVIACIÓN</t>
+          <t>RF-05 Chiclla</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1003,19 +1011,19 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS LPDC-01 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS RF-05 Chiclla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LPDC-01 LIXIVIACIÓN</t>
+          <t>RF-05 Chiclla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1027,12 +1035,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>03648883</t>
+          <t>03649223</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LPDC-02 LIXIVIACIÓN</t>
+          <t>RF-05 Chiclla</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1041,19 +1049,19 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS LPDC-02 LIXIVIACIÓN</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS RF-05 Chiclla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>LPDC-02 LIXIVIACIÓN</t>
+          <t>RF-05 Chiclla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1065,12 +1073,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>03648884</t>
+          <t>03649224</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LPDC-02 LIXIVIACIÓN</t>
+          <t>CGP PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1079,19 +1087,19 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46207</v>
+        <v>46129</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS LPDC-02 LIXIVIACIÓN</t>
+          <t>MONITOREO DE BAÑOS Y CASINOS CGP PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>LPDC-02 LIXIVIACIÓN</t>
+          <t>CGP PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1103,12 +1111,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>03648885</t>
+          <t>03677147</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LPDC-03 LIXIVIACIÓN</t>
+          <t>CPPCHE PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1117,19 +1125,19 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46207</v>
+        <v>46129</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS LPDC-03 LIXIVIACIÓN</t>
+          <t>MONITOREO DE BAÑOS Y CASINOS CPPCHE PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>LPDC-03 LIXIVIACIÓN</t>
+          <t>CPPCHE PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1141,12 +1149,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>03648886</t>
+          <t>03677148</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LPDC-03 LIXIVIACIÓN</t>
+          <t>CGP PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1155,19 +1163,19 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46207</v>
+        <v>46129</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS LPDC-03 LIXIVIACIÓN</t>
+          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES CGP PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>LPDC-03 LIXIVIACIÓN</t>
+          <t>CGP PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1179,12 +1187,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>03648887</t>
+          <t>03677149</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LPDC-04 LIXIVIACIÓN</t>
+          <t>CPPCHE PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1193,19 +1201,19 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46207</v>
+        <v>46129</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS LPDC-04 LIXIVIACIÓN</t>
+          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES CPPCHE PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>LPDC-04 LIXIVIACIÓN</t>
+          <t>CPPCHE PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1217,88 +1225,80 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>03648888</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>LPDC-04 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03675515</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS LPDC-04 LIXIVIACIÓN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>LPDC-04 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>OPERACIÓN ESTACIONES METEOROLOGICAS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>03648889</t>
+          <t>03678603</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LPDC-05 LIXIVIACIÓN</t>
+          <t>Estacion Calidad del aire Puerto</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46207</v>
+        <v>46132</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS LPDC-05 LIXIVIACIÓN</t>
+          <t>OPERACIÓN DE ESTACIONES CONTINUAS Estacion Calidad del aire Puerto</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>LPDC-05 LIXIVIACIÓN</t>
+          <t>Estacion Calidad del aire Puerto</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>03648890</t>
+          <t>03661667</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LPDC-05 LIXIVIACIÓN</t>
+          <t>R-B-2 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS LPDC-05 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS R-B-2 COPOSA NORTE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>LPDC-05 LIXIVIACIÓN</t>
+          <t>R-B-2 COPOSA NORTE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1331,12 +1331,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>03648891</t>
+          <t>03661668</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LPDC-06 LIXIVIACIÓN</t>
+          <t>R-C-1 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1345,19 +1345,19 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS LPDC-06 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) R-C-1 COPOSA NORTE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>LPDC-06 LIXIVIACIÓN</t>
+          <t>R-C-1 COPOSA NORTE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1369,12 +1369,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>03648892</t>
+          <t>03661669</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LPDC-06 LIXIVIACIÓN</t>
+          <t>R-C-2 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1383,19 +1383,19 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS LPDC-06 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) R-C-2 COPOSA NORTE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>LPDC-06 LIXIVIACIÓN</t>
+          <t>R-C-2 COPOSA NORTE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1407,12 +1407,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>03648893</t>
+          <t>03661670</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LPDC-07 LIXIVIACIÓN</t>
+          <t>R-C-3B  COPOSA NORTE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1421,19 +1421,19 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS LPDC-07 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) R-C-3B  COPOSA NORTE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>LPDC-07 LIXIVIACIÓN</t>
+          <t>R-C-3B  COPOSA NORTE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1445,12 +1445,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>03648894</t>
+          <t>03661671</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LPDC-07 LIXIVIACIÓN</t>
+          <t>R-PORT-1 PORTEZUELO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS LPDC-07 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) R-PORT-1 PORTEZUELO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>LPDC-07 LIXIVIACIÓN</t>
+          <t>R-PORT-1 PORTEZUELO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>03648895</t>
+          <t>03661672</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LPDC-08 LIXIVIACIÓN</t>
+          <t>PEP-04C PORTEZUELO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1497,19 +1497,19 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS LPDC-08 LIXIVIACIÓN</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PEP-04C PORTEZUELO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>LPDC-08 LIXIVIACIÓN</t>
+          <t>PEP-04C PORTEZUELO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1521,12 +1521,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>03648896</t>
+          <t>03661673</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LPDC-08 LIXIVIACIÓN</t>
+          <t>PEP-04C PORTEZUELO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1535,19 +1535,19 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS LPDC-08 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PEP-04C PORTEZUELO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>LPDC-08 LIXIVIACIÓN</t>
+          <t>PEP-04C PORTEZUELO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1559,12 +1559,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>03649005</t>
+          <t>03661674</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>P-4B MICHINCHA</t>
+          <t>PEP-03 PORTEZUELO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1573,19 +1573,19 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS P-4B MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PEP-03 PORTEZUELO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>P-4B MICHINCHA</t>
+          <t>PEP-03 PORTEZUELO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1597,12 +1597,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>03649006</t>
+          <t>03661675</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>P-4B MICHINCHA</t>
+          <t>PEP-03 PORTEZUELO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) P-4B MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PEP-03 PORTEZUELO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>P-4B MICHINCHA</t>
+          <t>PEP-03 PORTEZUELO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>03649007</t>
+          <t>03661743</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RPW-3 LIXIVIACIÓN</t>
+          <t>CWE-25 (2) COPOSA NORTE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1649,19 +1649,19 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS RPW-3 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) CWE-25 (2) COPOSA NORTE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>RPW-3 LIXIVIACIÓN</t>
+          <t>CWE-25 (2) COPOSA NORTE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1673,12 +1673,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>03649008</t>
+          <t>03661744</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RPW-3 LIXIVIACIÓN</t>
+          <t>CWE-25 (3) COPOSA NORTE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1687,19 +1687,19 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) RPW-3 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) CWE-25 (3) COPOSA NORTE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>RPW-3 LIXIVIACIÓN</t>
+          <t>CWE-25 (3) COPOSA NORTE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1711,12 +1711,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>03649009</t>
+          <t>03661754</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RPW-4 LIXIVIACIÓN</t>
+          <t>CWE-07 COPOSA SUR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1725,19 +1725,19 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS RPW-4 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) CWE-07 COPOSA SUR</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>RPW-4 LIXIVIACIÓN</t>
+          <t>CWE-07 COPOSA SUR</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1749,12 +1749,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>03649010</t>
+          <t>03661779</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RPW-4 LIXIVIACIÓN</t>
+          <t>PEC-02 PORTEZUELO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1763,19 +1763,19 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) RPW-4 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PEC-02 PORTEZUELO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>RPW-4 LIXIVIACIÓN</t>
+          <t>PEC-02 PORTEZUELO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1787,12 +1787,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>03649011</t>
+          <t>03661780</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RPW-1 LIXIVIACIÓN</t>
+          <t>PEP-02  PORTEZUELO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1801,19 +1801,19 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS RPW-1 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PEP-02  PORTEZUELO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>RPW-1 LIXIVIACIÓN</t>
+          <t>PEP-02  PORTEZUELO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1825,12 +1825,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>03649012</t>
+          <t>03661783</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RPW-1 LIXIVIACIÓN</t>
+          <t>PPC-01A COPOSA NORTE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) RPW-1 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PPC-01A COPOSA NORTE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>RPW-1 LIXIVIACIÓN</t>
+          <t>PPC-01A COPOSA NORTE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1863,12 +1863,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>03649013</t>
+          <t>03661784</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>P-6 MICHINCHA</t>
+          <t>PPC-02 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1877,19 +1877,19 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS P-6 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PPC-02 COPOSA NORTE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>P-6 MICHINCHA</t>
+          <t>PPC-02 COPOSA NORTE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1901,12 +1901,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>03649014</t>
+          <t>03661785</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>P-6 MICHINCHA</t>
+          <t>PPC-07 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS P-6 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PPC-07 COPOSA NORTE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>P-6 MICHINCHA</t>
+          <t>PPC-07 COPOSA NORTE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1939,12 +1939,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>03649015</t>
+          <t>03661786</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RPW-2  TRANQUE</t>
+          <t>PPC-09 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1953,19 +1953,19 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS RPW-2  TRANQUE</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PPC-09 COPOSA NORTE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>RPW-2  TRANQUE</t>
+          <t>PPC-09 COPOSA NORTE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1977,12 +1977,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>03649016</t>
+          <t>03661787</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RPW-2  TRANQUE</t>
+          <t>PPC-10 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS RPW-2  TRANQUE</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PPC-10 COPOSA NORTE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>RPW-2  TRANQUE</t>
+          <t>PPC-10 COPOSA NORTE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2015,12 +2015,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>03649017</t>
+          <t>03661788</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CSW-02 JACHUCOPOSA</t>
+          <t>PPC-14 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2029,19 +2029,19 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES CSW-02 JACHUCOPOSA</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PPC-14 COPOSA NORTE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CSW-02 JACHUCOPOSA</t>
+          <t>PPC-14 COPOSA NORTE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2053,12 +2053,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>03649024</t>
+          <t>03661789</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CPMA-01 JACHUCOPOSA</t>
+          <t>PPC-15 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2067,19 +2067,19 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS CPMA-01 JACHUCOPOSA</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PPC-15 COPOSA NORTE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CPMA-01 JACHUCOPOSA</t>
+          <t>PPC-15 COPOSA NORTE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>03649040</t>
+          <t>03661790</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>M-13 MICHINCHA</t>
+          <t>PPC-20 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2105,19 +2105,19 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS M-13 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PPC-20 COPOSA NORTE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>M-13 MICHINCHA</t>
+          <t>PPC-20 COPOSA NORTE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2129,12 +2129,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>03649041</t>
+          <t>03661791</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>M-13 MICHINCHA</t>
+          <t>PPC-21 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2143,19 +2143,19 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS M-13 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PPC-21 COPOSA NORTE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>M-13 MICHINCHA</t>
+          <t>PPC-21 COPOSA NORTE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2167,12 +2167,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>03649042</t>
+          <t>03661792</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>M-16 MICHINCHA</t>
+          <t>PPC-29 COPOSA NORTE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2181,19 +2181,19 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS M-16 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PPC-29 COPOSA NORTE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>M-16 MICHINCHA</t>
+          <t>PPC-29 COPOSA NORTE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>03649043</t>
+          <t>03661826</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>M-16 MICHINCHA</t>
+          <t>PEP-01 PORTEZUELO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2219,19 +2219,19 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS M-16 MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PEP-01 PORTEZUELO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>M-16 MICHINCHA</t>
+          <t>PEP-01 PORTEZUELO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2243,12 +2243,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>03649044</t>
+          <t>03661827</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>M-17 MICHINCHA</t>
+          <t>PEP-01 PORTEZUELO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2257,19 +2257,19 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS M-17 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PEP-01 PORTEZUELO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>M-17 MICHINCHA</t>
+          <t>PEP-01 PORTEZUELO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2281,12 +2281,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>03649045</t>
+          <t>03661830</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>M-17 MICHINCHA</t>
+          <t>RF-3 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2295,19 +2295,19 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS M-17 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) RF-3 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>M-17 MICHINCHA</t>
+          <t>RF-3 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2319,12 +2319,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>03649046</t>
+          <t>03661831</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>M-18 MICHINCHA</t>
+          <t>RF-3 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2333,19 +2333,19 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS M-18 MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS RF-3 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>M-18 MICHINCHA</t>
+          <t>RF-3 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2357,164 +2357,148 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>03649047</t>
+          <t>03661846</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>M-18 MICHINCHA</t>
+          <t>DE AGUA. Lisimetro/Evaporimetro</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS M-18 MICHINCHA</t>
+          <t>MEDICION DE EVAPOTRANSPIRACION Y EVAPORA DE AGUA. Lisimetro/Evaporimetro</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>M-18 MICHINCHA</t>
+          <t>DE AGUA. Lisimetro/Evaporimetro</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>03649048</t>
+          <t>03661848</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>M-19 MICHINCHA</t>
+          <t>DE AGUA. Lisimetro/Evaporimetro</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS M-19 MICHINCHA</t>
+          <t>MEDICION DE EVAPOTRANSPIRACION Y EVAPORA DE AGUA. Lisimetro/Evaporimetro</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>M-19 MICHINCHA</t>
+          <t>DE AGUA. Lisimetro/Evaporimetro</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>03649062</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>MAU-13 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03670809</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46207</v>
+        <v>46132</v>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MAU-13 LIXIVIACIÓN</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>MAU-13 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>OPERACIÓN DE ESTACIONES CONTINUAS</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>03649063</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>MAU-02 MICHINCHA</t>
-        </is>
-      </c>
+          <t>03670810</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46207</v>
+        <v>46132</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MAU-02 MICHINCHA</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>MAU-02 MICHINCHA</t>
-        </is>
-      </c>
+          <t>MANTENCION DE ESTACIONES CONTINUAS</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>03649064</t>
+          <t>03668548</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MAU-02 MICHINCHA</t>
+          <t>MITIGACION JACHUCOPOSA (CP-03M)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2523,19 +2507,19 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MAU-02 MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MITIGACION JACHUCOPOSA (CP-03M)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MAU-02 MICHINCHA</t>
+          <t>MITIGACION JACHUCOPOSA (CP-03M)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2547,12 +2531,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>03649067</t>
+          <t>03668549</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MAU-13 LIXIVIACIÓN</t>
+          <t>CP-01-I FALLA PABELLON</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2561,19 +2545,19 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MAU-13 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS CP-01-I FALLA PABELLON</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>MAU-13 LIXIVIACIÓN</t>
+          <t>CP-01-I FALLA PABELLON</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2585,12 +2569,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>03649069</t>
+          <t>03668550</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MIT-01B LIXIVIACIÓN</t>
+          <t>CP-02-C FALLA PABELLON</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2599,19 +2583,19 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MIT-01B LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS CP-02-C FALLA PABELLON</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MIT-01B LIXIVIACIÓN</t>
+          <t>CP-02-C FALLA PABELLON</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2623,12 +2607,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>03649070</t>
+          <t>03668551</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MIT-02B LIXIVIACIÓN</t>
+          <t>CP-03-M FALLA PABELLON</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2637,19 +2621,19 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MIT-02B LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS CP-03-M FALLA PABELLON</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MIT-02B LIXIVIACIÓN</t>
+          <t>CP-03-M FALLA PABELLON</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2661,12 +2645,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>03649071</t>
+          <t>03668552</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MIT-03 LIXIVIACIÓN</t>
+          <t>CP-04-L FALLA PABELLON</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2675,19 +2659,19 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MIT-03 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS CP-04-L FALLA PABELLON</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>MIT-03 LIXIVIACIÓN</t>
+          <t>CP-04-L FALLA PABELLON</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2699,12 +2683,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>03649072</t>
+          <t>03668553</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MIT-01B LIXIVIACIÓN</t>
+          <t>CP-05-H FALLA PABELLON</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2713,19 +2697,19 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MIT-01B LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS CP-05-H FALLA PABELLON</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MIT-01B LIXIVIACIÓN</t>
+          <t>CP-05-H FALLA PABELLON</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2737,12 +2721,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>03649073</t>
+          <t>03668554</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MIT-02B LIXIVIACIÓN</t>
+          <t>CP-06-J FALLA PABELLON</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2751,19 +2735,19 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MIT-02B LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS CP-06-J FALLA PABELLON</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MIT-02B LIXIVIACIÓN</t>
+          <t>CP-06-J FALLA PABELLON</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2775,12 +2759,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>03649074</t>
+          <t>03668555</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MIT-03 LIXIVIACIÓN</t>
+          <t>CP-07-F FALLA PABELLON</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2789,19 +2773,19 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MIT-03 LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS CP-07-F FALLA PABELLON</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MIT-03 LIXIVIACIÓN</t>
+          <t>CP-07-F FALLA PABELLON</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2813,12 +2797,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>03649075</t>
+          <t>03668556</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MMA-01 MICHINCHA</t>
+          <t>CP-08-D FALLA PABELLON</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2827,19 +2811,19 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MMA-01 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CP-08-D FALLA PABELLON</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>MMA-01 MICHINCHA</t>
+          <t>CP-08-D FALLA PABELLON</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2851,12 +2835,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>03649076</t>
+          <t>03668557</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MMA-02 MICHINCHA</t>
+          <t>CP-09-G FALLA PABELLON</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2865,19 +2849,19 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MMA-02 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CP-09-G FALLA PABELLON</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MMA-02 MICHINCHA</t>
+          <t>CP-09-G FALLA PABELLON</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2889,12 +2873,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>03649077</t>
+          <t>03668558</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MMA-03 MICHINCHA</t>
+          <t>CP-10-B FALLA PABELLON</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2903,19 +2887,19 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MMA-03 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CP-10-B FALLA PABELLON</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>MMA-03 MICHINCHA</t>
+          <t>CP-10-B FALLA PABELLON</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2927,12 +2911,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>03649078</t>
+          <t>03668559</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MMA-04 MICHINCHA</t>
+          <t>CP-11-E FALLA PABELLON</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2941,19 +2925,19 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MMA-04 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CP-11-E FALLA PABELLON</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MMA-04 MICHINCHA</t>
+          <t>CP-11-E FALLA PABELLON</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2965,12 +2949,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>03649079</t>
+          <t>03668560</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MMA-05 MICHINCHA</t>
+          <t>CP-12-K FALLA PABELLON</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2979,19 +2963,19 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MMA-05 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CP-12-K FALLA PABELLON</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>MMA-05 MICHINCHA</t>
+          <t>CP-12-K FALLA PABELLON</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3003,12 +2987,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>03649080</t>
+          <t>03668561</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MMA-06 MICHINCHA</t>
+          <t>CP-13-A FALLA PABELLON</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3017,19 +3001,19 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E69" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MMA-06 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CP-13-A FALLA PABELLON</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MMA-06 MICHINCHA</t>
+          <t>CP-13-A FALLA PABELLON</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3041,12 +3025,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>03649081</t>
+          <t>03668562</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MMA-07 MICHINCHA</t>
+          <t>CPS-20 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3055,19 +3039,19 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E70" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MMA-07 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CPS-20 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MMA-07 MICHINCHA</t>
+          <t>CPS-20 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3079,12 +3063,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>03649082</t>
+          <t>03668563</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MMA-08 MICHINCHA</t>
+          <t>CPS-23 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3093,19 +3077,19 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E71" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MMA-08 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CPS-23 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MMA-08 MICHINCHA</t>
+          <t>CPS-23 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3117,12 +3101,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>03649083</t>
+          <t>03668564</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MMA-09 MICHINCHA</t>
+          <t>CPS-54 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3131,19 +3115,19 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E72" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MMA-09 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CPS-54 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MMA-09 MICHINCHA</t>
+          <t>CPS-54 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3155,12 +3139,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>03649084</t>
+          <t>03668565</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MMA-10 MICHINCHA</t>
+          <t>CPS-55 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3169,19 +3153,19 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MMA-10 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CPS-55 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MMA-10 MICHINCHA</t>
+          <t>CPS-55 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3193,12 +3177,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>03649085</t>
+          <t>03668566</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MMA-11 MICHINCHA</t>
+          <t>CPZ-08C JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3207,19 +3191,19 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MMA-11 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CPZ-08C JACHUCOPOSA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MMA-11 MICHINCHA</t>
+          <t>CPZ-08C JACHUCOPOSA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3231,12 +3215,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>03649086</t>
+          <t>03668574</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MMA-12 MICHINCHA</t>
+          <t>CPZ-07A JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3245,19 +3229,19 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MMA-12 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CPZ-07A JACHUCOPOSA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MMA-12 MICHINCHA</t>
+          <t>CPZ-07A JACHUCOPOSA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3269,12 +3253,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>03649087</t>
+          <t>03668575</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MMA-13 MICHINCHA</t>
+          <t>CWE-12 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3283,19 +3267,19 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E76" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MMA-13 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CWE-12 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MMA-13 MICHINCHA</t>
+          <t>CWE-12 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3307,12 +3291,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>03649088</t>
+          <t>03668579</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MMA-14 MICHINCHA</t>
+          <t>CWE-01 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3321,19 +3305,19 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E77" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MMA-14 MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS CWE-01 FALLA PABELLON</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MMA-14 MICHINCHA</t>
+          <t>CWE-01 FALLA PABELLON</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3345,12 +3329,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>03649089</t>
+          <t>03668581</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MMA-01 MICHINCHA</t>
+          <t>CWE-06 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3359,19 +3343,19 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E78" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MMA-01 MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS CWE-06 FALLA PABELLON</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>MMA-01 MICHINCHA</t>
+          <t>CWE-06 FALLA PABELLON</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3383,12 +3367,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>03649090</t>
+          <t>03668584</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MMA-02 MICHINCHA</t>
+          <t>CWE-12 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3397,19 +3381,19 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E79" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MMA-02 MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS CWE-12 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>MMA-02 MICHINCHA</t>
+          <t>CWE-12 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3421,12 +3405,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>03649091</t>
+          <t>03668585</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MMA-03 MICHINCHA</t>
+          <t>CWE-19 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3435,19 +3419,19 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E80" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MMA-03 MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS CWE-19 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MMA-03 MICHINCHA</t>
+          <t>CWE-19 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3459,12 +3443,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>03649092</t>
+          <t>03668591</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MMA-04 MICHINCHA</t>
+          <t>CWE-01 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3473,19 +3457,19 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E81" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MMA-04 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CWE-01 FALLA PABELLON</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MMA-04 MICHINCHA</t>
+          <t>CWE-01 FALLA PABELLON</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3497,12 +3481,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>03649093</t>
+          <t>03668592</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MMA-05 MICHINCHA</t>
+          <t>CWE-06 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3511,19 +3495,19 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MMA-05 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CWE-06 FALLA PABELLON</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>MMA-05 MICHINCHA</t>
+          <t>CWE-06 FALLA PABELLON</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3535,12 +3519,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>03649094</t>
+          <t>03668594</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MMA-06 MICHINCHA</t>
+          <t>CWP-14 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3549,19 +3533,19 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MMA-06 MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS CWP-14 FALLA PABELLON</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>MMA-06 MICHINCHA</t>
+          <t>CWP-14 FALLA PABELLON</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3573,12 +3557,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>03649095</t>
+          <t>03668595</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MMA-07 MICHINCHA</t>
+          <t>CWP-14 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3587,19 +3571,19 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E84" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MMA-07 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS CWP-14 FALLA PABELLON</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>MMA-07 MICHINCHA</t>
+          <t>CWP-14 FALLA PABELLON</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3611,50 +3595,50 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>03649096</t>
+          <t>03668596</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MMA-08 MICHINCHA</t>
+          <t>DEC-06B COPOSA SUR</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGVANC</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E85" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MMA-08 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS DEC-06B COPOSA SUR</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MMA-08 MICHINCHA</t>
+          <t>DEC-06B COPOSA SUR</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGVANC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>03649097</t>
+          <t>03668599</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MMA-09 MICHINCHA</t>
+          <t>JCC-4 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3663,19 +3647,19 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MMA-09 MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES JCC-4 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>MMA-09 MICHINCHA</t>
+          <t>JCC-4 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3687,12 +3671,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>03649098</t>
+          <t>03668600</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MMA-10 MICHINCHA</t>
+          <t>JCC-5 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3701,19 +3685,19 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E87" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MMA-10 MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES JCC-5 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>MMA-10 MICHINCHA</t>
+          <t>JCC-5 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3725,12 +3709,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>03649099</t>
+          <t>03668601</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MMA-11 MICHINCHA</t>
+          <t>M-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3739,19 +3723,19 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E88" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MMA-11 MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS M-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MMA-11 MICHINCHA</t>
+          <t>M-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3763,12 +3747,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>03649100</t>
+          <t>03668602</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MMA-12 MICHINCHA</t>
+          <t>M-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3777,19 +3761,19 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E89" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MMA-12 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS M-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>MMA-12 MICHINCHA</t>
+          <t>M-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3801,50 +3785,50 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>03649101</t>
+          <t>03668603</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MMA-13 MICHINCHA</t>
+          <t>MA-08 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGVANC</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MMA-13 MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MA-08 FALLA PABELLON</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>MMA-13 MICHINCHA</t>
+          <t>MA-08 FALLA PABELLON</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGVANC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>03649102</t>
+          <t>03668604</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MMA-14 MICHINCHA</t>
+          <t>MAU-01B LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3853,19 +3837,19 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MMA-14 MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MAU-01B LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>MMA-14 MICHINCHA</t>
+          <t>MAU-01B LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3877,12 +3861,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>03649103</t>
+          <t>03668605</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MPZ-10A LIXIVIACIÓN</t>
+          <t>MAU-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3891,19 +3875,19 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MPZ-10A LIXIVIACIÓN</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MAU-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>MPZ-10A LIXIVIACIÓN</t>
+          <t>MAU-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3915,12 +3899,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>03649104</t>
+          <t>03668606</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MPZ-10B LIXIVIACIÓN</t>
+          <t>MAU-01B LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3929,19 +3913,19 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MPZ-10B LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS MAU-01B LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>MPZ-10B LIXIVIACIÓN</t>
+          <t>MAU-01B LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3953,12 +3937,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>03649105</t>
+          <t>03668607</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MPZ-11B MICHINCHA</t>
+          <t>MAU-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3967,19 +3951,19 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MPZ-11B MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS MAU-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>MPZ-11B MICHINCHA</t>
+          <t>MAU-12 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -3991,12 +3975,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>03649106</t>
+          <t>03668608</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MPZ-11B MICHINCHA</t>
+          <t>MTP-11 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4005,19 +3989,19 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MPZ-11B MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS MTP-11 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>MPZ-11B MICHINCHA</t>
+          <t>MTP-11 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4029,12 +4013,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>03649109</t>
+          <t>03668609</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MPZ-10A LIXIVIACIÓN</t>
+          <t>MTP-11 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4043,19 +4027,19 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E96" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MPZ-10A LIXIVIACIÓN</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MTP-11 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>MPZ-10A LIXIVIACIÓN</t>
+          <t>MTP-11 LIXIVIACIÓN</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4067,12 +4051,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>03649110</t>
+          <t>03668610</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MPZ-10B LIXIVIACIÓN</t>
+          <t>MTP-15 TRANQUE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4081,19 +4065,19 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E97" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS MPZ-10B LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS MTP-15 TRANQUE</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>MPZ-10B LIXIVIACIÓN</t>
+          <t>MTP-15 TRANQUE</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4105,12 +4089,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>03649111</t>
+          <t>03668611</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MSW-1A MICHINCHA</t>
+          <t>MTP-16 TRANQUE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4119,19 +4103,19 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E98" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES MSW-1A MICHINCHA</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MTP-16 TRANQUE</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>MSW-1A MICHINCHA</t>
+          <t>MTP-16 TRANQUE</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4143,12 +4127,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>03649112</t>
+          <t>03668612</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MSW-2 MICHINCHA</t>
+          <t>MTP-20 TRANQUE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4157,19 +4141,19 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E99" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES MSW-2 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS MTP-20 TRANQUE</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MSW-2 MICHINCHA</t>
+          <t>MTP-20 TRANQUE</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4181,12 +4165,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>03649113</t>
+          <t>03668613</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MSW-2 MICHINCHA</t>
+          <t>MTP-16 TRANQUE</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4195,19 +4179,19 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E100" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MEDICIÓN DE CAUDALES MSW-2 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS MTP-16 TRANQUE</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>MSW-2 MICHINCHA</t>
+          <t>MTP-16 TRANQUE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4219,12 +4203,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>03649114</t>
+          <t>03668620</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MTP-13 MICHINCHA</t>
+          <t>PMA-03 UJINA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4233,19 +4217,19 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E101" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) MTP-13 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS PMA-03 UJINA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MTP-13 MICHINCHA</t>
+          <t>PMA-03 UJINA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4257,12 +4241,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>03649115</t>
+          <t>03668625</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MTP-13 MICHINCHA</t>
+          <t>PQY-02 YABRICOYITA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4271,19 +4255,19 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E102" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MTP-13 MICHINCHA</t>
+          <t>MEDICION DE NIVELES FREATICOS PQY-02 YABRICOYITA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>MTP-13 MICHINCHA</t>
+          <t>PQY-02 YABRICOYITA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4295,12 +4279,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>03649116</t>
+          <t>03668626</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MTP-09 TRANQUE</t>
+          <t>PQY-03 YABRICOYITA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4309,19 +4293,19 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E103" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) MTP-09 TRANQUE</t>
+          <t>MEDICION DE NIVELES FREATICOS PQY-03 YABRICOYITA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>MTP-09 TRANQUE</t>
+          <t>PQY-03 YABRICOYITA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4333,12 +4317,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>03649117</t>
+          <t>03668627</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MTP-09 TRANQUE</t>
+          <t>QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4347,19 +4331,19 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E104" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MTP-09 TRANQUE</t>
+          <t>MEDICIÓN DE CAUDALES QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>MTP-09 TRANQUE</t>
+          <t>QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4371,12 +4355,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>03649118</t>
+          <t>03668628</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MTP-14 TRANQUE</t>
+          <t>QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4385,19 +4369,19 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E105" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) MTP-14 TRANQUE</t>
+          <t>MEDICIÓN DE CAUDALES QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>MTP-14 TRANQUE</t>
+          <t>QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4409,12 +4393,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>03649119</t>
+          <t>03668633</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MTP-14 TRANQUE</t>
+          <t>SH-19 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4423,19 +4407,19 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E106" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS MTP-14 TRANQUE</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS SH-19 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>MTP-14 TRANQUE</t>
+          <t>SH-19 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4447,12 +4431,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>03649127</t>
+          <t>03668634</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PLIX-01A LIXIVIACIÓN</t>
+          <t>SH-20 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4461,19 +4445,19 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E107" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-01A LIXIVIACIÓN</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS SH-20 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>PLIX-01A LIXIVIACIÓN</t>
+          <t>SH-20 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4485,12 +4469,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>03649128</t>
+          <t>03668635</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PLIX-01B LIXIVIACIÓN</t>
+          <t>SH-22 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4499,19 +4483,19 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E108" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-01B LIXIVIACIÓN</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS SH-22 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>PLIX-01B LIXIVIACIÓN</t>
+          <t>SH-22 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4523,12 +4507,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>03649129</t>
+          <t>03668636</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PLIX-02A LIXIVIACIÓN</t>
+          <t>SH-23 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4537,19 +4521,19 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E109" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-02A LIXIVIACIÓN</t>
+          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS SH-23 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>PLIX-02A LIXIVIACIÓN</t>
+          <t>SH-23 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4561,12 +4545,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>03649130</t>
+          <t>03668637</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PLIX-02B LIXIVIACIÓN</t>
+          <t>SH-20 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4575,19 +4559,19 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E110" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-02B LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS SH-20 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>PLIX-02B LIXIVIACIÓN</t>
+          <t>SH-20 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4599,12 +4583,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>03649131</t>
+          <t>03668638</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PLIX-03A LIXIVIACIÓN</t>
+          <t>SH-22 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4613,19 +4597,19 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E111" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-03A LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS SH-22 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>PLIX-03A LIXIVIACIÓN</t>
+          <t>SH-22 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4637,12 +4621,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>03649132</t>
+          <t>03668639</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PLIX-03B LIXIVIACIÓN</t>
+          <t>SH-23 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4651,19 +4635,19 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E112" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-03B LIXIVIACIÓN</t>
+          <t>MEDICION DE NIVELES FREATICOS SH-23 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>PLIX-03B LIXIVIACIÓN</t>
+          <t>SH-23 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4675,12 +4659,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>03649133</t>
+          <t>03668640</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PLIX-04 LIXIVIACIÓN</t>
+          <t>Piscina P2 ROSARIO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4689,19 +4673,19 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E113" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-04 LIXIVIACIÓN</t>
+          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES Piscina P2 ROSARIO</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>PLIX-04 LIXIVIACIÓN</t>
+          <t>Piscina P2 ROSARIO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4713,12 +4697,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>03649134</t>
+          <t>03668641</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PLIX-05A LIXIVIACIÓN</t>
+          <t>ARR- 1 (Piscina P2)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4727,19 +4711,19 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E114" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-05A LIXIVIACIÓN</t>
+          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES ARR- 1 (Piscina P2)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>PLIX-05A LIXIVIACIÓN</t>
+          <t>ARR- 1 (Piscina P2)</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4751,12 +4735,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>03649135</t>
+          <t>03668645</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PLIX-05B LIXIVIACIÓN</t>
+          <t>Piscina P3 ROSARIO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4765,19 +4749,19 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E115" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-05B LIXIVIACIÓN</t>
+          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES Piscina P3 ROSARIO</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>PLIX-05B LIXIVIACIÓN</t>
+          <t>Piscina P3 ROSARIO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4789,301 +4773,253 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>03649136</t>
+          <t>03670812</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PLIX-06 LIXIVIACIÓN</t>
+          <t>Casino 460</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E116" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-06 LIXIVIACIÓN</t>
+          <t>MANTENCION DE ESTACIONES CONTINUAS Casino 460</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>PLIX-06 LIXIVIACIÓN</t>
+          <t>Casino 460</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>03649137</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>PLIX-07A LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03671634</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E117" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-07A LIXIVIACIÓN</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>PLIX-07A LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>REPORTE BBDD MP</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>03649138</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>PLIX-07B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03671635</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E118" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-07B LIXIVIACIÓN</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>PLIX-07B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>REPORTE CALIDAD CWS-02 Y MITIGACIÓN JACH</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>03649139</t>
+          <t>03671636</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PLIX-08A LIXIVIACIÓN</t>
+          <t>REPORTE PAT FRONTERA (Dashboard nivel y cauda</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E119" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-08A LIXIVIACIÓN</t>
+          <t>REPORTE PAT FRONTERA (Dashboard nivel y REPORTE PAT FRONTERA (Dashboard nivel y cauda</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>PLIX-08A LIXIVIACIÓN</t>
+          <t>REPORTE PAT FRONTERA (Dashboard nivel y cauda</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>03649140</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>PLIX-08B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03671637</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E120" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-08B LIXIVIACIÓN</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>PLIX-08B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>REPORTE BBDD QDH-02</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>03649141</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>PLIX-09 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03671638</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E121" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-09 LIXIVIACIÓN</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>PLIX-09 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>REPORTE CALIDAD DE AIRE (TODAS ESTACIONE</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>03649142</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>PLIX-10A LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03671639</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46207</v>
+        <v>46128</v>
       </c>
       <c r="E122" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-10A LIXIVIACIÓN</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>PLIX-10A LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>PPT RED CALIDAD DE AIRE</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>03649143</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>PLIX-10B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03686123</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
           <t>SIGVA</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E123" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-10B LIXIVIACIÓN</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>PLIX-10B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>MEDICION DE NIVELES FREATICOS</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>SIGVA</t>
@@ -5093,35 +5029,27 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>03649144</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>PLIX-11A LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03686126</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
           <t>SIGVA</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E124" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-11A LIXIVIACIÓN</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>PLIX-11A LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>MEDICION DE NIVELES FREATICOS</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>SIGVA</t>
@@ -5131,35 +5059,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>03649145</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>PLIX-11B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03686127</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
           <t>SIGVA</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E125" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-11B LIXIVIACIÓN</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>PLIX-11B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>MEDICION DE NIVELES FREATICOS</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>SIGVA</t>
@@ -5169,35 +5089,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>03649146</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>PLIX-12B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03686128</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
           <t>SIGVA</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E126" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-12B LIXIVIACIÓN</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>PLIX-12B LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>MEDICION DE NIVELES FREATICOS</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>SIGVA</t>
@@ -5207,35 +5119,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>03649147</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>PLIX-13A LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03686137</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
           <t>SIGVA</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E127" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-13A LIXIVIACIÓN</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>PLIX-13A LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>MEDICION DE NIVELES FREATICOS</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>SIGVA</t>
@@ -5245,12 +5149,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>03649148</t>
+          <t>03676987</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PLIX-13B LIXIVIACIÓN</t>
+          <t>OFICINAS  SI ENERGIA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5259,19 +5163,19 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E128" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-13B LIXIVIACIÓN</t>
+          <t>HOUSEKEEPING OFICINAS  SI ENERGIA</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>PLIX-13B LIXIVIACIÓN</t>
+          <t>OFICINAS  SI ENERGIA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5283,12 +5187,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>03649149</t>
+          <t>03676988</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PLIX-14 LIXIVIACIÓN</t>
+          <t>BCON UJINA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5297,19 +5201,19 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E129" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PLIX-14 LIXIVIACIÓN</t>
+          <t>MONITOREO DE BAÑOS Y CASINOS BCON UJINA</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>PLIX-14 LIXIVIACIÓN</t>
+          <t>BCON UJINA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5321,12 +5225,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>03649150</t>
+          <t>03676989</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PLIX-01A LIXIVIACIÓN</t>
+          <t>BGSO UJINA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5335,19 +5239,19 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E130" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-01A LIXIVIACIÓN</t>
+          <t>MONITOREO DE BAÑOS Y CASINOS BGSO UJINA</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>PLIX-01A LIXIVIACIÓN</t>
+          <t>BGSO UJINA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5359,12 +5263,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>03649151</t>
+          <t>03676990</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PLIX-01B LIXIVIACIÓN</t>
+          <t>ZANJA NORTE 2 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5373,19 +5277,19 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E131" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-01B LIXIVIACIÓN</t>
+          <t>MEDICIÓN NIVELES FREÁTICOS ZANJA NORTE 2 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>PLIX-01B LIXIVIACIÓN</t>
+          <t>ZANJA NORTE 2 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5397,12 +5301,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>03649152</t>
+          <t>03676991</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PLIX-02A LIXIVIACIÓN</t>
+          <t>PTAS PUERTO COLLAHUASI PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5411,19 +5315,19 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E132" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-02A LIXIVIACIÓN</t>
+          <t>MONITOREO AGUAS SERVIDAS PTAS PUERTO COLLAHUASI PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>PLIX-02A LIXIVIACIÓN</t>
+          <t>PTAS PUERTO COLLAHUASI PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5435,12 +5339,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>03649153</t>
+          <t>03676992</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PLIX-02B LIXIVIACIÓN</t>
+          <t>ZANJA NORTE 1 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5449,19 +5353,19 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E133" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-02B LIXIVIACIÓN</t>
+          <t>MEDICIÓN NIVELES FREÁTICOS ZANJA NORTE 1 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>PLIX-02B LIXIVIACIÓN</t>
+          <t>ZANJA NORTE 1 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5473,12 +5377,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>03649154</t>
+          <t>03676993</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PLIX-03A LIXIVIACIÓN</t>
+          <t>PTAS-C FALLA PABELLON</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5487,19 +5391,19 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E134" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-03A LIXIVIACIÓN</t>
+          <t>MUESTREO PUNTUAL DE RIL AS PTAS-C FALLA PABELLON</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>PLIX-03A LIXIVIACIÓN</t>
+          <t>PTAS-C FALLA PABELLON</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5511,12 +5415,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>03649155</t>
+          <t>03676994</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PLIX-03B LIXIVIACIÓN</t>
+          <t>TK-505 FALLA PABELLON</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5525,19 +5429,19 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E135" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-03B LIXIVIACIÓN</t>
+          <t>MONITOREO EN SALAS DE ESTACION Y TK TK-505 FALLA PABELLON</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>PLIX-03B LIXIVIACIÓN</t>
+          <t>TK-505 FALLA PABELLON</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5549,12 +5453,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>03649156</t>
+          <t>03676995</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PLIX-04 LIXIVIACIÓN</t>
+          <t>CSW-02 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5563,19 +5467,19 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E136" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-04 LIXIVIACIÓN</t>
+          <t>MEDICIÓN CAUDALES CSW-02 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>PLIX-04 LIXIVIACIÓN</t>
+          <t>CSW-02 JACHUCOPOSA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5587,12 +5491,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>03649157</t>
+          <t>03676996</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PLIX-05A LIXIVIACIÓN</t>
+          <t>BPCR ROSARIO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5601,19 +5505,19 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E137" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-05A LIXIVIACIÓN</t>
+          <t>MONITOREO DE BAÑOS Y CASINOS BPCR ROSARIO</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>PLIX-05A LIXIVIACIÓN</t>
+          <t>BPCR ROSARIO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5625,12 +5529,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>03649158</t>
+          <t>03676997</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PLIX-05B LIXIVIACIÓN</t>
+          <t>QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5639,19 +5543,19 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E138" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-05B LIXIVIACIÓN</t>
+          <t>MUESTREO  M. AGUAS  SUPERF (FOTOMETRO) QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>PLIX-05B LIXIVIACIÓN</t>
+          <t>QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5663,12 +5567,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>03649159</t>
+          <t>03676998</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PLIX-06 LIXIVIACIÓN</t>
+          <t>QDH-2 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5677,19 +5581,19 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E139" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-06 LIXIVIACIÓN</t>
+          <t>MEDICIÓN CAUDALES QDH-2 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>PLIX-06 LIXIVIACIÓN</t>
+          <t>QDH-2 HUINQUINTIPA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5701,12 +5605,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>03649160</t>
+          <t>03676999</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PLIX-07A LIXIVIACIÓN</t>
+          <t>QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5715,19 +5619,19 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E140" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-07A LIXIVIACIÓN</t>
+          <t>MUESTREO  M. AGUAS  SUPERF. (FOTOMETRO) QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>PLIX-07A LIXIVIACIÓN</t>
+          <t>QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5739,12 +5643,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>03649161</t>
+          <t>03677000</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PLIX-07B LIXIVIACIÓN</t>
+          <t>QSN-1 SAN NICOLAS</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5753,19 +5657,19 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E141" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-07B LIXIVIACIÓN</t>
+          <t>MEDICIÓN CAUDALES QSN-1 SAN NICOLAS</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>PLIX-07B LIXIVIACIÓN</t>
+          <t>QSN-1 SAN NICOLAS</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5777,12 +5681,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>03649162</t>
+          <t>03677001</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PLIX-08A LIXIVIACIÓN</t>
+          <t>SH-02B PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5791,19 +5695,19 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E142" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-08A LIXIVIACIÓN</t>
+          <t>MEDICIÓN NIVELES FREÁTICOS SH-02B PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>PLIX-08A LIXIVIACIÓN</t>
+          <t>SH-02B PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5815,12 +5719,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>03649163</t>
+          <t>03677002</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PLIX-08B LIXIVIACIÓN</t>
+          <t>SH-06 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5829,19 +5733,19 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E143" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-08B LIXIVIACIÓN</t>
+          <t>MEDICIÓN NIVELES FREÁTICOS SH-06 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>PLIX-08B LIXIVIACIÓN</t>
+          <t>SH-06 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5853,12 +5757,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>03649164</t>
+          <t>03677003</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PLIX-09 LIXIVIACIÓN</t>
+          <t>SH-07 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5867,19 +5771,19 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E144" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-09 LIXIVIACIÓN</t>
+          <t>MEDICIÓN NIVELES FREÁTICOS SH-07 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>PLIX-09 LIXIVIACIÓN</t>
+          <t>SH-07 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5891,12 +5795,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>03649165</t>
+          <t>03677004</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PLIX-10A LIXIVIACIÓN</t>
+          <t>SH-08 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5905,19 +5809,19 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E145" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-10A LIXIVIACIÓN</t>
+          <t>MEDICIÓN NIVELES FREÁTICOS SH-08 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>PLIX-10A LIXIVIACIÓN</t>
+          <t>SH-08 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -5929,12 +5833,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>03649166</t>
+          <t>03677005</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PLIX-10B LIXIVIACIÓN</t>
+          <t>SH-19 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5943,19 +5847,19 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E146" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-10B LIXIVIACIÓN</t>
+          <t>MEDICIÓN NIVELES FREÁTICOS SH-19 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>PLIX-10B LIXIVIACIÓN</t>
+          <t>SH-19 PUERTO COLLAHUASI</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5967,12 +5871,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>03649167</t>
+          <t>03677006</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PLIX-11A LIXIVIACIÓN</t>
+          <t>CPC FALLA PABELLON</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5981,19 +5885,19 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E147" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-11A LIXIVIACIÓN</t>
+          <t>MONITOREO DE BAÑOS Y CASINOS CPC FALLA PABELLON</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>PLIX-11A LIXIVIACIÓN</t>
+          <t>CPC FALLA PABELLON</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6005,12 +5909,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>03649168</t>
+          <t>03677007</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PLIX-11B LIXIVIACIÓN</t>
+          <t>C-1000 UJINA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6019,19 +5923,19 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E148" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-11B LIXIVIACIÓN</t>
+          <t>MONITOREO DE BAÑOS Y CASINOS C-1000 UJINA</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>PLIX-11B LIXIVIACIÓN</t>
+          <t>C-1000 UJINA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6043,12 +5947,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>03649169</t>
+          <t>03677008</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PLIX-12B LIXIVIACIÓN</t>
+          <t>MONITOREO DE BAÑOS Y CASINOS BCC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -6057,19 +5961,19 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E149" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-12B LIXIVIACIÓN</t>
+          <t>MONITOREO DE BAÑOS Y CASINOS MONITOREO DE BAÑOS Y CASINOS BCC</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>PLIX-12B LIXIVIACIÓN</t>
+          <t>MONITOREO DE BAÑOS Y CASINOS BCC</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6081,12 +5985,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>03649170</t>
+          <t>03677009</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PLIX-13A LIXIVIACIÓN</t>
+          <t>C-460 ROSARIO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -6095,19 +5999,19 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E150" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-13A LIXIVIACIÓN</t>
+          <t>MONITOREO DE BAÑOS Y CASINOS C-460 ROSARIO</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>PLIX-13A LIXIVIACIÓN</t>
+          <t>C-460 ROSARIO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6119,12 +6023,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>03649171</t>
+          <t>03677010</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PLIX-13B LIXIVIACIÓN</t>
+          <t>CCD</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -6133,19 +6037,19 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E151" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-13B LIXIVIACIÓN</t>
+          <t>MONITOREO DE BAÑOS Y CASINOS CCD</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>PLIX-13B LIXIVIACIÓN</t>
+          <t>CCD</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6157,12 +6061,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>03649172</t>
+          <t>03677011</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PLIX-14 LIXIVIACIÓN</t>
+          <t>TK-1004 ROSARIO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6171,19 +6075,19 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E152" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS PLIX-14 LIXIVIACIÓN</t>
+          <t>MONITOREO EN SALAS DE ESTACION Y TK TK-1004 ROSARIO</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>PLIX-14 LIXIVIACIÓN</t>
+          <t>TK-1004 ROSARIO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6195,12 +6099,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>03649179</t>
+          <t>03677012</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PMI-01 MICHINCHA</t>
+          <t>TK-517 UJINA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6209,19 +6113,19 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E153" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS (PAT EIA) PMI-01 MICHINCHA</t>
+          <t>MONITOREO EN SALAS DE ESTACION Y TK TK-517 UJINA</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>PMI-01 MICHINCHA</t>
+          <t>TK-517 UJINA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6233,12 +6137,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>03649180</t>
+          <t>03677013</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PMI-01 MICHINCHA</t>
+          <t>PTAS-M ROSARIO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -6247,19 +6151,19 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E154" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS PMI-01 MICHINCHA</t>
+          <t>MUESTREO PUNTUAL DE RIL-AS PTAS-M ROSARIO</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>PMI-01 MICHINCHA</t>
+          <t>PTAS-M ROSARIO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6271,12 +6175,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>03649185</t>
+          <t>03677014</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PR  PUERTO COLLAHUASI</t>
+          <t>BOR ROSARIO</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6285,19 +6189,19 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E155" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES PR  PUERTO COLLAHUASI</t>
+          <t>MONITOREO DE BAÑOS Y CASINOS BOR ROSARIO</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>PR  PUERTO COLLAHUASI</t>
+          <t>BOR ROSARIO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6309,12 +6213,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>03649186</t>
+          <t>03677015</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
+          <t>PISCINA  DIQUE HUINQUINTIPA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6323,19 +6227,19 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E156" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>MEDICIÓN DE CAUDALES QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
+          <t>MUESTREO  M. AGUAS  SUPERF (FOTOMETRO) PISCINA  DIQUE HUINQUINTIPA</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
+          <t>PISCINA  DIQUE HUINQUINTIPA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6347,2848 +6251,1058 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>03649188</t>
+          <t>03679194</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
+          <t>Ujina</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E157" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>MEDICIÓN DE CAUDALES QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
+          <t>OPERACIÓN DE ESTACIONES CONTINUAS Ujina</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
+          <t>Ujina</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>03649206</t>
+          <t>03679195</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Estación 1</t>
+          <t>Ujina</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E158" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES Estación 1</t>
+          <t>OPERACIÓN DE ESTACIONES DISCRETAS Ujina</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Estación 1</t>
+          <t>Ujina</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>03649207</t>
+          <t>03679196</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Piscina P3 ROSARIO</t>
+          <t>Coposa Continuo</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E159" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES Piscina P3 ROSARIO</t>
+          <t>OPERACIÓN DE ESTACIONES CONTINUAS Coposa Continuo</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Piscina P3 ROSARIO</t>
+          <t>Coposa Continuo</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>03649216</t>
+          <t>03679197</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LPDC-09 LIXIVIACIÓN</t>
+          <t>Coposa EMRP Discreto</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E160" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS LPDC-09 LIXIVIACIÓN</t>
+          <t>OPERACIÓN DE ESTACIONES DISCRETAS Coposa EMRP Discreto</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>LPDC-09 LIXIVIACIÓN</t>
+          <t>Coposa EMRP Discreto</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>03649217</t>
+          <t>03679236</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LPDC-09 LIXIVIACIÓN</t>
+          <t>Casino 460</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E161" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS LPDC-09 LIXIVIACIÓN</t>
+          <t>OPERACIÓN DE ESTACIONES CONTINUAS Casino 460</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>LPDC-09 LIXIVIACIÓN</t>
+          <t>Casino 460</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGAIR</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>03649218</t>
+          <t>03679237</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>LPDC-10 LIXIVIACIÓN</t>
+          <t>IQUIQUE - CMDIC Y VICE VERSA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGADM</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E162" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS LPDC-10 LIXIVIACIÓN</t>
+          <t>TRASLADO PERS. Y CAM. TURNO CONTRATOS IQUIQUE - CMDIC Y VICE VERSA</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>LPDC-10 LIXIVIACIÓN</t>
+          <t>IQUIQUE - CMDIC Y VICE VERSA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGADM</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>03649219</t>
+          <t>03679238</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LPDC-10 LIXIVIACIÓN</t>
+          <t>IQUIQUE - CMDIC Y VICE VERSA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGADM</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E163" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS LPDC-10 LIXIVIACIÓN</t>
+          <t>TRASLADO MUESTRAS Y MATERIAL MUESTREO IQUIQUE - CMDIC Y VICE VERSA</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>LPDC-10 LIXIVIACIÓN</t>
+          <t>IQUIQUE - CMDIC Y VICE VERSA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGADM</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>03649220</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>LPDC-11 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03679277</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46207</v>
+        <v>46129</v>
       </c>
       <c r="E164" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUBTERRÁNEAS LPDC-11 LIXIVIACIÓN</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>LPDC-11 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>REPORTE INFORMES PDR</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>03649221</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>LPDC-11 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>03679278</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46207</v>
+        <v>46129</v>
       </c>
       <c r="E165" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS LPDC-11 LIXIVIACIÓN</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>LPDC-11 LIXIVIACIÓN</t>
-        </is>
-      </c>
+          <t>REPORTE PLANILLA NIVELES</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>03649238</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>PAR PUERTO COLLAHUASI</t>
-        </is>
-      </c>
+          <t>03679279</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46207</v>
+        <v>46129</v>
       </c>
       <c r="E166" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES PAR PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>PAR PUERTO COLLAHUASI</t>
-        </is>
-      </c>
+          <t>REPORTE PLANILLA CAUDALES</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>03649239</t>
+          <t>03687291</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PEV-01 (PES-01) PUERTO COLLAHUASI</t>
+          <t>BODEGA SIGA-B02</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGAIR</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E167" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES PEV-01 (PES-01) PUERTO COLLAHUASI</t>
+          <t>GESTION DE RESIDUOS BODEGA SIGA-B02</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>PEV-01 (PES-01) PUERTO COLLAHUASI</t>
+          <t>BODEGA SIGA-B02</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGAIR</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>03649240</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>CWE-18 (1) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>03687292</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGADM</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E168" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS CWE-18 (1) FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>CWE-18 (1) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>HOUSEKEEPING</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGADM</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>03649241</t>
+          <t>03687293</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CWE-18 (2) FALLA PABELLON</t>
+          <t>PISCINA DIQUE SAN DANIEL</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGVA</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46207</v>
+        <v>46134</v>
       </c>
       <c r="E169" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS CWE-18 (2) FALLA PABELLON</t>
+          <t>MUESTREO  M. AGUAS  SUPERF. (FOTOMETRO) PISCINA DIQUE SAN DANIEL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>CWE-18 (2) FALLA PABELLON</t>
+          <t>PISCINA DIQUE SAN DANIEL</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGVA</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>03649242</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>CWE-23 (1) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>03679280</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46207</v>
+        <v>46130</v>
       </c>
       <c r="E170" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS CWE-23 (1) FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>CWE-23 (1) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>INFORME NARICES ELECTRÓNICAS</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>03649243</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>CWE-23 (2) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>03679281</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E171" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS CWE-23 (2) FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>CWE-23 (2) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>REPORTE PLANILLA NIVELES MENSUAL (PMA)</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>03649244</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>CWE-23 (3) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>03679282</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E172" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS CWE-23 (3) FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>CWE-23 (3) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>REPORTE PLANILLA Q HORARIO (PMA)</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>03649245</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>CWE-23 (4) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>03679283</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E173" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS CWE-23 (4) FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>CWE-23 (4) FALLA PABELLON</t>
-        </is>
-      </c>
+          <t>REPORTE PLANILLA Q DIARIO (PMA)</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>03649246</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>M-09 MICHINCHA</t>
-        </is>
-      </c>
+          <t>03679284</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E174" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS M-09 MICHINCHA</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>M-09 MICHINCHA</t>
-        </is>
-      </c>
+          <t>REPORTE PLANILLA Q MENSUAL (PMA)</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>03649247</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>M-28 MICHINCHA</t>
-        </is>
-      </c>
+          <t>03679285</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E175" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS M-28 MICHINCHA</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>M-28 MICHINCHA</t>
-        </is>
-      </c>
+          <t>REPORTE RES 31</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>03649248</t>
+          <t>03679286</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>UC-602 LIXIVIACIÓN</t>
+          <t>REPORTE POZOS  MICHINCHA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E176" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS UC-602 LIXIVIACIÓN</t>
+          <t>REPORTE POZOS  MICHINCHA REPORTE POZOS  MICHINCHA</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>UC-602 LIXIVIACIÓN</t>
+          <t>REPORTE POZOS  MICHINCHA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>03649249</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>UC-603 MICHINCHA</t>
-        </is>
-      </c>
+          <t>03679287</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E177" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS UC-603 MICHINCHA</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>UC-603 MICHINCHA</t>
-        </is>
-      </c>
+          <t>MM1: Anexo CAUDAL SUPERFICIAL</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>SIGVANC</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>03653640</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr"/>
+          <t>03679288</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>MM1: Dashboard niveles</t>
+        </is>
+      </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SIGEXT</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E178" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>INSPECCION DE EXTINTOR SALIMAX</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr"/>
+          <t>MM1: Dashboard niveles MM1: Dashboard niveles</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>MM1: Dashboard niveles</t>
+        </is>
+      </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>SIGEXT</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>03653641</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr"/>
+          <t>03679289</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>REPORTE POZOS PUERTO</t>
+        </is>
+      </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SIGEXT</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E179" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>INSPECCIÓN EXTINTOR CALIDAD AIRE COPOSA</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr"/>
+          <t>REPORTE POZOS PUERTO REPORTE POZOS PUERTO</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>REPORTE POZOS PUERTO</t>
+        </is>
+      </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>SIGEXT</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>03653642</t>
+          <t>03679290</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SIGEXT</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E180" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>INSPECCIÓN EXTINTOR ALS UJINA</t>
+          <t>REPORTE PLANILLA NIVELES</t>
         </is>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
-          <t>SIGEXT</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>03660793</t>
+          <t>03679291</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46207</v>
+        <v>46133</v>
       </c>
       <c r="E181" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>MEDICION DE NIVELES FREATICOS (PAT EIA)</t>
+          <t>REPORTE PLANILLA CAUDALES</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>03648737</t>
+          <t>03679292</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>IQUIQUE - CMDIC Y VICE VERSA</t>
+          <t>REPORTE PISCINAS P3-P2</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>SIGADM</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46238</v>
+        <v>46133</v>
       </c>
       <c r="E182" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>TRASLADO PERS. Y CAM. TURNO CONTRATOS IQUIQUE - CMDIC Y VICE VERSA</t>
+          <t>REPORTE PISCINAS P3-P2 REPORTE PISCINAS P3-P2</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>IQUIQUE - CMDIC Y VICE VERSA</t>
+          <t>REPORTE PISCINAS P3-P2</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>SIGADM</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>03648738</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>IQUIQUE - CMDIC Y VICE VERSA</t>
-        </is>
-      </c>
+          <t>03679293</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>SIGADM</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46238</v>
+        <v>46133</v>
       </c>
       <c r="E183" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>TRASLADO MUESTRAS Y MATERIAL MUESTREO IQUIQUE - CMDIC Y VICE VERSA</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>IQUIQUE - CMDIC Y VICE VERSA</t>
-        </is>
-      </c>
+          <t>INFORME DE RUIDO</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
-          <t>SIGADM</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>03661637</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>OFICINAS  SI ENERGIA</t>
-        </is>
-      </c>
+          <t>03679294</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46238</v>
+        <v>46134</v>
       </c>
       <c r="E184" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>HOUSEKEEPING OFICINAS  SI ENERGIA</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>OFICINAS  SI ENERGIA</t>
-        </is>
-      </c>
+          <t>REPORTE PAT BARRERA HIDRÁULICA</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>03661638</t>
+          <t>03679295</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>BCON UJINA</t>
+          <t>REPORTE PAT JACHUCOPOSA-COPOSITO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46238</v>
+        <v>46134</v>
       </c>
       <c r="E185" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS BCON UJINA</t>
+          <t>REPORTE PAT JACHUCOPOSA-COPOSITO REPORTE PAT JACHUCOPOSA-COPOSITO</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>BCON UJINA</t>
+          <t>REPORTE PAT JACHUCOPOSA-COPOSITO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>03661639</t>
+          <t>03679296</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>BGSO UJINA</t>
+          <t>REPORTE PAT TRANQUE</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46238</v>
+        <v>46134</v>
       </c>
       <c r="E186" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS BGSO UJINA</t>
+          <t>REPORTE PAT TRANQUE REPORTE PAT TRANQUE</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>BGSO UJINA</t>
+          <t>REPORTE PAT TRANQUE</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>03661640</t>
+          <t>ES532MACWE          0001</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ZANJA NORTE 2 PUERTO COLLAHUASI</t>
+          <t>REPORTE BALANCE IONICO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46238</v>
+        <v>46134</v>
       </c>
       <c r="E187" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>MEDICIÓN NIVELES FREÁTICOS ZANJA NORTE 2 PUERTO COLLAHUASI</t>
+          <t>REPORTE BALANCE IONICO REPORTE BALANCE IONICO</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>ZANJA NORTE 2 PUERTO COLLAHUASI</t>
+          <t>REPORTE BALANCE IONICO</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>03661641</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>PTAS PUERTO COLLAHUASI PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D188" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E188" t="n">
-        <v>4</v>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>MONITOREO AGUAS SERVIDAS PTAS PUERTO COLLAHUASI PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>PTAS PUERTO COLLAHUASI PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>03661642</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>ZANJA NORTE 1 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D189" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E189" t="n">
-        <v>4</v>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>MEDICIÓN NIVELES FREÁTICOS ZANJA NORTE 1 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>ZANJA NORTE 1 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>03661643</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>PTAS-C FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D190" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E190" t="n">
-        <v>4</v>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>MUESTREO PUNTUAL DE RIL AS PTAS-C FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>PTAS-C FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>03661644</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>TK-505 FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D191" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E191" t="n">
-        <v>4</v>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>MONITOREO EN SALAS DE ESTACION Y TK TK-505 FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>TK-505 FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>03661645</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>CSW-02 JACHUCOPOSA</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D192" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E192" t="n">
-        <v>4</v>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>MEDICIÓN CAUDALES CSW-02 JACHUCOPOSA</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>CSW-02 JACHUCOPOSA</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>03661646</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>BPCR ROSARIO</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D193" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E193" t="n">
-        <v>4</v>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS BPCR ROSARIO</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>BPCR ROSARIO</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>03661647</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D194" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E194" t="n">
-        <v>4</v>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>MUESTREO  M. AGUAS  SUPERF (FOTOMETRO) QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>QDH-1E PISC. HUINQUIN. (INT. RAJO ROSA )</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>03661648</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>QDH-2 HUINQUINTIPA</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D195" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E195" t="n">
-        <v>4</v>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>MEDICIÓN CAUDALES QDH-2 HUINQUINTIPA</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>QDH-2 HUINQUINTIPA</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>03661649</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D196" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E196" t="n">
-        <v>4</v>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>MUESTREO  M. AGUAS  SUPERF. (FOTOMETRO) QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>QSD-1 PISC. HUINQUIN. (INT. RAJO ROSA )</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>03661650</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>QSN-1 SAN NICOLAS</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D197" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E197" t="n">
-        <v>4</v>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>MEDICIÓN CAUDALES QSN-1 SAN NICOLAS</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>QSN-1 SAN NICOLAS</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>03661651</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>SH-02B PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D198" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E198" t="n">
-        <v>4</v>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>MEDICIÓN NIVELES FREÁTICOS SH-02B PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>SH-02B PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>03661652</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>SH-06 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D199" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E199" t="n">
-        <v>4</v>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>MEDICIÓN NIVELES FREÁTICOS SH-06 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>SH-06 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>03661653</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>SH-07 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D200" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E200" t="n">
-        <v>4</v>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>MEDICIÓN NIVELES FREÁTICOS SH-07 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>SH-07 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>03661654</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>SH-08 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D201" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E201" t="n">
-        <v>4</v>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>MEDICIÓN NIVELES FREÁTICOS SH-08 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>SH-08 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>03661655</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>SH-19 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D202" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E202" t="n">
-        <v>4</v>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>MEDICIÓN NIVELES FREÁTICOS SH-19 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>SH-19 PUERTO COLLAHUASI</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>03661656</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>CPC FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D203" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E203" t="n">
-        <v>4</v>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS CPC FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>CPC FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>03661657</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>C-1000 UJINA</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D204" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E204" t="n">
-        <v>4</v>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS C-1000 UJINA</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>C-1000 UJINA</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>03661658</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS BCC</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D205" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E205" t="n">
-        <v>4</v>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS MONITOREO DE BAÑOS Y CASINOS BCC</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS BCC</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>03661659</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>C-460 ROSARIO</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D206" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E206" t="n">
-        <v>4</v>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS C-460 ROSARIO</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>C-460 ROSARIO</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>03661660</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>CCD</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D207" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E207" t="n">
-        <v>4</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS CCD</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>CCD</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>03661661</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>TK-1004 ROSARIO</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D208" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E208" t="n">
-        <v>4</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>MONITOREO EN SALAS DE ESTACION Y TK TK-1004 ROSARIO</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>TK-1004 ROSARIO</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>03661662</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>TK-517 UJINA</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D209" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E209" t="n">
-        <v>4</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>MONITOREO EN SALAS DE ESTACION Y TK TK-517 UJINA</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>TK-517 UJINA</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>03661663</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>PTAS-M ROSARIO</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D210" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E210" t="n">
-        <v>4</v>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>MUESTREO PUNTUAL DE RIL-AS PTAS-M ROSARIO</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>PTAS-M ROSARIO</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>03661664</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>BOR ROSARIO</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D211" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E211" t="n">
-        <v>4</v>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS BOR ROSARIO</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>BOR ROSARIO</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>03661665</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>PISCINA  DIQUE HUINQUINTIPA</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D212" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E212" t="n">
-        <v>4</v>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>MUESTREO  M. AGUAS  SUPERF (FOTOMETRO) PISCINA  DIQUE HUINQUINTIPA</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>PISCINA  DIQUE HUINQUINTIPA</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>03661838</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Ujina</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-      <c r="D213" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E213" t="n">
-        <v>4</v>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>OPERACIÓN DE ESTACIONES CONTINUAS Ujina</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Ujina</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>03661839</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Ujina</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-      <c r="D214" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E214" t="n">
-        <v>4</v>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>OPERACIÓN DE ESTACIONES DISCRETAS Ujina</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>Ujina</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>03661840</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Coposa Continuo</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-      <c r="D215" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E215" t="n">
-        <v>4</v>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>OPERACIÓN DE ESTACIONES CONTINUAS Coposa Continuo</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Coposa Continuo</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>03661841</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Coposa EMRP Discreto</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-      <c r="D216" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E216" t="n">
-        <v>4</v>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>OPERACIÓN DE ESTACIONES DISCRETAS Coposa EMRP Discreto</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>Coposa EMRP Discreto</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>03661842</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Casino 460</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-      <c r="D217" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E217" t="n">
-        <v>4</v>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>OPERACIÓN DE ESTACIONES CONTINUAS Casino 460</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>Casino 460</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>03670028</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>BODEGA SIGA-B02</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-      <c r="D218" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E218" t="n">
-        <v>4</v>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>GESTION DE RESIDUOS BODEGA SIGA-B02</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>BODEGA SIGA-B02</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>SIGAIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>03670029</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr"/>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>SIGADM</t>
-        </is>
-      </c>
-      <c r="D219" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E219" t="n">
-        <v>4</v>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>HOUSEKEEPING</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>SIGADM</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>03670030</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>PISCINA DIQUE SAN DANIEL</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D220" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E220" t="n">
-        <v>4</v>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>MUESTREO  M. AGUAS  SUPERF. (FOTOMETRO) PISCINA DIQUE SAN DANIEL</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>PISCINA DIQUE SAN DANIEL</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>03649225</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>BCON UJINA</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D221" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E221" t="n">
-        <v>4</v>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES BCON UJINA</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>BCON UJINA</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>03649226</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>BGSO UJINA</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D222" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E222" t="n">
-        <v>4</v>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES BGSO UJINA</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>BGSO UJINA</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>03649227</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>TK-505 FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D223" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E223" t="n">
-        <v>4</v>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES TK-505 FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>TK-505 FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>03649228</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>BPCR ROSARIO</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D224" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E224" t="n">
-        <v>4</v>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES BPCR ROSARIO</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>BPCR ROSARIO</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>03649229</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>CPC FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D225" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E225" t="n">
-        <v>4</v>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES CPC FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>CPC FALLA PABELLON</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>03649230</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>C-1000 UJINA</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D226" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E226" t="n">
-        <v>4</v>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES C-1000 UJINA</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>C-1000 UJINA</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>03649231</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS BCC</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D227" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E227" t="n">
-        <v>4</v>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES MONITOREO DE BAÑOS Y CASINOS BCC</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>MONITOREO DE BAÑOS Y CASINOS BCC</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>03649232</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>C-460 ROSARIO</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D228" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E228" t="n">
-        <v>4</v>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES C-460 ROSARIO</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>C-460 ROSARIO</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>03649233</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>CCD</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D229" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E229" t="n">
-        <v>4</v>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES CCD</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>CCD</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>03649234</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>TK-1004 ROSARIO</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D230" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E230" t="n">
-        <v>4</v>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES TK-1004 ROSARIO</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>TK-1004 ROSARIO</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>03649235</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>TK-517 UJINA</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D231" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E231" t="n">
-        <v>4</v>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES TK-517 UJINA</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>TK-517 UJINA</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>03649236</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>BOR ROSARIO</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
-        </is>
-      </c>
-      <c r="D232" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="E232" t="n">
-        <v>4</v>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>MUESTREO MANUAL DE AGUAS SUPERFICIALES BOR ROSARIO</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>BOR ROSARIO</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>SIGVA</t>
+          <t>SIGRPMO</t>
         </is>
       </c>
     </row>
